--- a/content/horarios.xlsx
+++ b/content/horarios.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="108">
   <si>
     <t>Dia</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>Salsa, Bachata</t>
-  </si>
-  <si>
-    <t>mishel_fernandez.jpg</t>
   </si>
   <si>
     <t>Giusmary</t>
@@ -727,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1155,45 +1152,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="A10:A55">
@@ -1222,13 +1180,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1423,25 +1381,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="B10:B36">
@@ -1452,7 +1391,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1686,9 +1625,6 @@
       <c r="C10" t="s">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
@@ -1704,7 +1640,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1727,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1750,7 +1686,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
@@ -1773,7 +1709,7 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
         <v>29</v>
@@ -1796,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -1819,7 +1755,7 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
@@ -1842,13 +1778,13 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -1862,7 +1798,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1877,10 +1813,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,44 +1824,44 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
         <v>96</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
         <v>98</v>
-      </c>
-      <c r="B5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
         <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -1933,10 +1869,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
         <v>103</v>
-      </c>
-      <c r="B8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1944,7 +1880,7 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1952,19 +1888,19 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
         <v>107</v>
-      </c>
-      <c r="B11" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/content/horarios.xlsx
+++ b/content/horarios.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="109">
   <si>
     <t>Dia</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>Sexy Style</t>
+  </si>
+  <si>
+    <t>Por confirmar</t>
   </si>
   <si>
     <t>21:00</t>
@@ -854,7 +857,7 @@
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -874,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -897,19 +900,19 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -920,7 +923,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -946,7 +949,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -955,10 +958,10 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -972,7 +975,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -984,7 +987,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -998,19 +1001,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -1024,22 +1027,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -1050,13 +1053,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -1071,12 +1074,12 @@
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -1085,10 +1088,10 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1102,7 +1105,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
@@ -1111,7 +1114,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -1128,7 +1131,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -1137,7 +1140,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -1154,28 +1157,28 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="A10:A55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="A10:A55">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="A2:A55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="A2:A55">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="D10:D55">
-      <formula1>"Salsa,Bachata,Jazz,Latin Urban,Ladies,Ballet,Urban Style,Mambo,Body Movement,Urban Dance,Sexy Style,Sexy Power,Comercial Dance,Heels,Reggaeton,Ensayo Elenco"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="D10:D55">
+      <formula1>Generos!$A$2:$A$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="D2:D55">
-      <formula1>"Salsa,Bachata,Jazz,Latin Urban,Ladies,Ballet,Urban Style,Mambo,Body Movement,Urban Dance,Sexy Style,Sexy Power,Comercial Dance,Heels,Reggaeton,Ensayo Elenco"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="D2:D55">
+      <formula1>Generos!$A$2:$A$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="E10:E55">
-      <formula1>"Izquierdo,Joan,Martinez,Kike,Pedro,Stefanie,Mary,Estrella,Mishel Fernández,Giusmary Sosa,Vannia Valdivia,Edson Cabanillas,Kenneth Ocaña,Omar López,Anthony Sevillano,Gonzalo Povis"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="E10:E55">
+      <formula1>Profesores!$A$2:$A$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="E2:E55">
-      <formula1>"Izquierdo,Joan,Martinez,Kike,Pedro,Stefanie,Mary,Estrella,Mishel Fernández,Giusmary Sosa,Vannia Valdivia,Edson Cabanillas,Kenneth Ocaña,Omar López,Anthony Sevillano,Gonzalo Povis"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="E2:E55">
+      <formula1>Profesores!$A$2:$A$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="F10:F55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="F10:F55">
       <formula1>"Principiantes,Básico,Intermedio,Avanzado,All levels"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="F2:F55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="F2:F55">
       <formula1>"Principiantes,Básico,Intermedio,Avanzado,All levels"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1186,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1196,21 +1199,21 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1218,10 +1221,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1229,10 +1232,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -1240,10 +1243,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -1251,10 +1254,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1262,10 +1265,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1273,10 +1276,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
@@ -1284,10 +1287,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -1295,10 +1298,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -1309,7 +1312,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -1320,7 +1323,7 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -1331,7 +1334,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1339,10 +1342,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -1353,7 +1356,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1361,10 +1364,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -1372,21 +1375,22 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="B10:B36">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="B10:B36">
       <formula1>"Clase,Ensayo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elegí una opción de la lista." sqref="B2:B36">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="B2:B36">
       <formula1>"Clase,Ensayo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1397,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1410,39 +1414,39 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -1456,16 +1460,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -1479,16 +1483,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -1502,16 +1506,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1525,16 +1529,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -1548,16 +1552,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -1571,16 +1575,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -1594,16 +1598,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -1617,13 +1621,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -1640,7 +1644,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1663,7 +1667,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1686,7 +1690,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
@@ -1706,13 +1710,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -1729,13 +1733,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1752,13 +1756,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>43</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -1775,16 +1779,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -1796,6 +1800,18 @@
         <v>15</v>
       </c>
     </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -1813,55 +1829,55 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -1869,34 +1885,34 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/content/horarios.xlsx
+++ b/content/horarios.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="110">
   <si>
     <t>Dia</t>
   </si>
@@ -61,34 +61,37 @@
     <t>Sala 1</t>
   </si>
   <si>
+    <t>Prueba de publicación</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>Sexy Power</t>
+  </si>
+  <si>
+    <t>Vannia Valdivia</t>
+  </si>
+  <si>
+    <t>All levels</t>
+  </si>
+  <si>
+    <t>Pack Noches</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>Heels</t>
+  </si>
+  <si>
+    <t>Edson Cabanillas</t>
+  </si>
+  <si>
+    <t>Básico</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>Sexy Power</t>
-  </si>
-  <si>
-    <t>Vannia Valdivia</t>
-  </si>
-  <si>
-    <t>All levels</t>
-  </si>
-  <si>
-    <t>Pack Noches</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>Heels</t>
-  </si>
-  <si>
-    <t>Edson Cabanillas</t>
-  </si>
-  <si>
-    <t>Básico</t>
   </si>
   <si>
     <t>Martes</t>
@@ -840,24 +843,24 @@
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -866,24 +869,24 @@
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -892,38 +895,38 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -944,12 +947,12 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -958,10 +961,10 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -975,19 +978,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -996,24 +999,24 @@
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -1022,44 +1025,44 @@
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -1074,12 +1077,12 @@
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -1088,10 +1091,10 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1105,7 +1108,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
@@ -1114,24 +1117,24 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -1140,19 +1143,19 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1199,112 +1202,112 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,21 +1315,21 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1334,21 +1337,21 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,35 +1359,34 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25"/>
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Valor no permitido" error="Elige una opción de la lista." sqref="B10:B36">
@@ -1401,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1414,229 +1416,229 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1644,22 +1646,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,22 +1669,22 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1690,128 +1692,127 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
         <v>36</v>
       </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -1829,90 +1830,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
